--- a/Result/profitability/3288.xlsx
+++ b/Result/profitability/3288.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04375000000000001</v>
+        <v>-0.01625000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>62.71</v>
+        <v>64.08625000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01750000000000001</v>
+        <v>-0.08625000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>59.69375</v>
+        <v>60.43375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05500000000000001</v>
+        <v>0.009999999999999995</v>
       </c>
       <c r="N4" t="n">
-        <v>56.63124999999999</v>
+        <v>59.69374999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.05</v>
       </c>
       <c r="M5" t="n">
-        <v>-8.673617379884035e-18</v>
+        <v>-0.008750000000000006</v>
       </c>
       <c r="N5" t="n">
-        <v>54.79499999999999</v>
+        <v>53.58625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.06375</v>
+        <v>-0.03875</v>
       </c>
       <c r="N6" t="n">
-        <v>48.805</v>
+        <v>50.07124999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.055</v>
       </c>
       <c r="N7" t="n">
-        <v>45.72749999999999</v>
+        <v>45.6675</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0525</v>
+        <v>-0.03875</v>
       </c>
       <c r="N8" t="n">
-        <v>41.23</v>
+        <v>40.49</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>-0.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0.009999999999999988</v>
+        <v>0.009999999999999992</v>
       </c>
       <c r="N10" t="n">
         <v>35.69625</v>
@@ -1772,7 +1772,7 @@
         <v>0.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04499999999999998</v>
+        <v>0.04499999999999999</v>
       </c>
       <c r="N11" t="n">
         <v>35.83125</v>
@@ -1899,7 +1899,7 @@
         <v>0.04</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01499999999999998</v>
+        <v>0.01499999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>34.67625</v>
@@ -2026,7 +2026,7 @@
         <v>-0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.003749999999999983</v>
+        <v>0.003749999999999989</v>
       </c>
       <c r="N13" t="n">
         <v>34.87625</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>21</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="n">
+        <v>15</v>
+      </c>
+      <c r="F75" t="n">
+        <v>71.04000000000001</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.09%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03875000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>66.60375000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.919999999999987</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07692307692307676</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.669999999999987</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1198116714161812</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
